--- a/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250606103858</t>
+    <t>20250611134354</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-06T10:38:58+01:00</t>
+    <t>2025-06-11T13:43:54+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250611134354</t>
+    <t>20250616134740</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-11T13:43:54+01:00</t>
+    <t>2025-06-16T13:47:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250616134740</t>
+    <t>20250624152101</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-16T13:47:40+01:00</t>
+    <t>2025-06-24T15:21:01+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
@@ -38,7 +38,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250624152101</t>
+    <t>20251216141840</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +68,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T15:21:01+01:00</t>
+    <t>2025-12-16T14:18:40+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -128,7 +128,7 @@
     <t>C547</t>
   </si>
   <si>
-    <t>Hormonothérapie</t>
+    <t>hormonothérapie</t>
   </si>
   <si>
     <t>C15262</t>
@@ -140,13 +140,13 @@
     <t>C63334</t>
   </si>
   <si>
-    <t>Radiologie interventionnelle</t>
+    <t>imagerie interventionnelle</t>
   </si>
   <si>
     <t>C157891</t>
   </si>
   <si>
-    <t>endoscopie interventionnelle</t>
+    <t>endoscopie peropératoire</t>
   </si>
   <si>
     <t>C15747</t>
@@ -167,7 +167,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/terminologie-ncit</t>
+    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
   </si>
   <si>
     <t>MED-556</t>

--- a/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
@@ -9,13 +9,12 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
     <sheet name="Include #1" r:id="rId5" sheetId="3"/>
-    <sheet name="Include #2" r:id="rId6" sheetId="4"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="68">
   <si>
     <t>Property</t>
   </si>
@@ -38,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251216141840</t>
+    <t>20260220142105</t>
   </si>
   <si>
     <t>Name</t>
@@ -68,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-16T14:18:40+01:00</t>
+    <t>2026-02-20T14:21:05+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -101,124 +100,121 @@
     <t>Concept</t>
   </si>
   <si>
-    <t>C15313</t>
+    <t>MED-556</t>
+  </si>
+  <si>
+    <t>Fenêtre thérapeutique</t>
+  </si>
+  <si>
+    <t>MED-226</t>
+  </si>
+  <si>
+    <t>Surveillance seule</t>
+  </si>
+  <si>
+    <t>MED-232</t>
+  </si>
+  <si>
+    <t>Irathérapie</t>
+  </si>
+  <si>
+    <t>MED-126</t>
+  </si>
+  <si>
+    <t>Allogreffe / Autogreffe</t>
+  </si>
+  <si>
+    <t>GEN-092.03.01</t>
+  </si>
+  <si>
+    <t>Autre(s) traitement(s)</t>
+  </si>
+  <si>
+    <t>GEN-092.03.02</t>
+  </si>
+  <si>
+    <t>Autre(s) traitement(s) médicamenteux spécifique(s)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>System URI</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
+  </si>
+  <si>
+    <t>387713003</t>
+  </si>
+  <si>
+    <t>intervention chirurgicale</t>
+  </si>
+  <si>
+    <t>1287742003</t>
   </si>
   <si>
     <t>radiothérapie</t>
   </si>
   <si>
-    <t>C15195</t>
+    <t>152198000</t>
   </si>
   <si>
     <t>curiethérapie</t>
   </si>
   <si>
-    <t>C15632</t>
+    <t>367336001</t>
   </si>
   <si>
     <t>chimiothérapie</t>
   </si>
   <si>
-    <t>C93352</t>
+    <t>1255831008</t>
   </si>
   <si>
     <t>thérapie ciblée</t>
   </si>
   <si>
-    <t>C547</t>
+    <t>169413002</t>
   </si>
   <si>
     <t>hormonothérapie</t>
   </si>
   <si>
-    <t>C15262</t>
+    <t>76334006</t>
   </si>
   <si>
     <t>immunothérapie</t>
   </si>
   <si>
-    <t>C63334</t>
+    <t>258174001</t>
   </si>
   <si>
     <t>imagerie interventionnelle</t>
   </si>
   <si>
-    <t>C157891</t>
-  </si>
-  <si>
-    <t>endoscopie peropératoire</t>
-  </si>
-  <si>
-    <t>C15747</t>
-  </si>
-  <si>
-    <t>soins de support</t>
-  </si>
-  <si>
-    <t>C15252</t>
-  </si>
-  <si>
-    <t>soins palliatifs</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>System URI</t>
-  </si>
-  <si>
-    <t>http://ncicb.nci.nih.gov/xml/owl/EVS/Thesaurus.owl</t>
-  </si>
-  <si>
-    <t>MED-556</t>
-  </si>
-  <si>
-    <t>Fenêtre thérapeutique</t>
-  </si>
-  <si>
-    <t>MED-226</t>
-  </si>
-  <si>
-    <t>Surveillance seule</t>
-  </si>
-  <si>
-    <t>MED-232</t>
-  </si>
-  <si>
-    <t>Irathérapie</t>
-  </si>
-  <si>
-    <t>MED-126</t>
-  </si>
-  <si>
-    <t>Allogreffe / Autogreffe</t>
-  </si>
-  <si>
-    <t>GEN-092.03.01</t>
-  </si>
-  <si>
-    <t>Autre(s) traitement(s)</t>
-  </si>
-  <si>
-    <t>GEN-092.03.02</t>
-  </si>
-  <si>
-    <t>Autre(s) traitement(s) médicamenteux spécifique(s)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/terminologie-cisis</t>
-  </si>
-  <si>
-    <t>387713003</t>
-  </si>
-  <si>
-    <t>intervention chirurgicale</t>
-  </si>
-  <si>
     <t>424313000</t>
   </si>
   <si>
     <t>surveillance active</t>
+  </si>
+  <si>
+    <t>363687006</t>
+  </si>
+  <si>
+    <t>endoscopie interventionnelle</t>
+  </si>
+  <si>
+    <t>243114000</t>
+  </si>
+  <si>
+    <t>soin de support</t>
+  </si>
+  <si>
+    <t>103735009</t>
+  </si>
+  <si>
+    <t>soin palliatif</t>
   </si>
   <si>
     <t>http://snomed.info/sct</t>
@@ -485,124 +481,6 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>27</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>32</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B5" t="s" s="2">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="s" s="2">
-        <v>36</v>
-      </c>
-      <c r="B6" t="s" s="2">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="s" s="2">
-        <v>38</v>
-      </c>
-      <c r="B7" t="s" s="2">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s" s="2">
-        <v>40</v>
-      </c>
-      <c r="B8" t="s" s="2">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s" s="2">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s" s="2">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="s" s="2">
-        <v>48</v>
-      </c>
-      <c r="B12" t="s" s="2">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="s" s="2">
-        <v>49</v>
-      </c>
-      <c r="B13" t="s" s="2">
-        <v>50</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
@@ -620,66 +498,66 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>52</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>54</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>59</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>60</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>62</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>48</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>63</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -687,9 +565,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:B15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -706,23 +584,23 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>65</v>
+        <v>44</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>66</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>67</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s" s="2">
         <v>48</v>
@@ -733,7 +611,87 @@
         <v>49</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>68</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B6" t="s" s="2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>55</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>57</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>63</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>65</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>40</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="2">
+        <v>41</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260220142105</t>
+    <t>20260311144904</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-20T14:21:05+01:00</t>
+    <t>2026-03-11T14:49:04+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260311144904</t>
+    <t>20260420150251</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T14:49:04+01:00</t>
+    <t>2026-04-20T15:02:51+01:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
+++ b/ig/main/ValueSet-jdv-type-traitement-frcp-cisis.xlsx
@@ -37,7 +37,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260420150251</t>
+    <t>20260619134043</t>
   </si>
   <si>
     <t>Name</t>
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T15:02:51+01:00</t>
+    <t>2026-06-19T13:40:43+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
